--- a/artfynd/A 6972-2022 artfynd.xlsx
+++ b/artfynd/A 6972-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6972-2022 artfynd.xlsx
+++ b/artfynd/A 6972-2022 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285680</v>
+        <v>121285681</v>
       </c>
       <c r="B3" t="n">
-        <v>97028</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517750</v>
+        <v>517751</v>
       </c>
       <c r="R3" t="n">
-        <v>6710311</v>
+        <v>6710312</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285681</v>
+        <v>121285680</v>
       </c>
       <c r="B4" t="n">
-        <v>57501</v>
+        <v>97038</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,25 +910,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517751</v>
+        <v>517750</v>
       </c>
       <c r="R4" t="n">
-        <v>6710312</v>
+        <v>6710311</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 6972-2022 artfynd.xlsx
+++ b/artfynd/A 6972-2022 artfynd.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Ellen Payne, Ursula Zinko</t>
+          <t>Ursula Zinko, Ellen Payne, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Ellen Payne, Ursula Zinko</t>
+          <t>Ursula Zinko, Ellen Payne, Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 6972-2022 artfynd.xlsx
+++ b/artfynd/A 6972-2022 artfynd.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Ellen Payne, Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Ellen Payne, Ursula Zinko</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -901,7 +901,7 @@
         <v>121285680</v>
       </c>
       <c r="B4" t="n">
-        <v>97038</v>
+        <v>97051</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ursula Zinko, Ellen Payne, Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Ellen Payne, Ursula Zinko</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 6972-2022 artfynd.xlsx
+++ b/artfynd/A 6972-2022 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285681</v>
+        <v>121285680</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>97052</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517751</v>
+        <v>517750</v>
       </c>
       <c r="R3" t="n">
-        <v>6710312</v>
+        <v>6710311</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285680</v>
+        <v>121285681</v>
       </c>
       <c r="B4" t="n">
-        <v>97051</v>
+        <v>57504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,25 +910,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517750</v>
+        <v>517751</v>
       </c>
       <c r="R4" t="n">
-        <v>6710311</v>
+        <v>6710312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 6972-2022 artfynd.xlsx
+++ b/artfynd/A 6972-2022 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285680</v>
+        <v>121285681</v>
       </c>
       <c r="B3" t="n">
-        <v>97052</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517750</v>
+        <v>517751</v>
       </c>
       <c r="R3" t="n">
-        <v>6710311</v>
+        <v>6710312</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285681</v>
+        <v>121285680</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
+        <v>97055</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,25 +910,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517751</v>
+        <v>517750</v>
       </c>
       <c r="R4" t="n">
-        <v>6710312</v>
+        <v>6710311</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 6972-2022 artfynd.xlsx
+++ b/artfynd/A 6972-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>121285681</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>121285680</v>
       </c>
       <c r="B4" t="n">
-        <v>97055</v>
+        <v>97061</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 6972-2022 artfynd.xlsx
+++ b/artfynd/A 6972-2022 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285681</v>
+        <v>121285680</v>
       </c>
       <c r="B3" t="n">
-        <v>57508</v>
+        <v>97061</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517751</v>
+        <v>517750</v>
       </c>
       <c r="R3" t="n">
-        <v>6710312</v>
+        <v>6710311</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285680</v>
+        <v>121285681</v>
       </c>
       <c r="B4" t="n">
-        <v>97061</v>
+        <v>57508</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,25 +910,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517750</v>
+        <v>517751</v>
       </c>
       <c r="R4" t="n">
-        <v>6710311</v>
+        <v>6710312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 6972-2022 artfynd.xlsx
+++ b/artfynd/A 6972-2022 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285680</v>
+        <v>121285681</v>
       </c>
       <c r="B3" t="n">
-        <v>97061</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517750</v>
+        <v>517751</v>
       </c>
       <c r="R3" t="n">
-        <v>6710311</v>
+        <v>6710312</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285681</v>
+        <v>121285680</v>
       </c>
       <c r="B4" t="n">
-        <v>57508</v>
+        <v>97062</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,25 +910,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517751</v>
+        <v>517750</v>
       </c>
       <c r="R4" t="n">
-        <v>6710312</v>
+        <v>6710311</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 6972-2022 artfynd.xlsx
+++ b/artfynd/A 6972-2022 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285681</v>
+        <v>121285680</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>97062</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517751</v>
+        <v>517750</v>
       </c>
       <c r="R3" t="n">
-        <v>6710312</v>
+        <v>6710311</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285680</v>
+        <v>121285681</v>
       </c>
       <c r="B4" t="n">
-        <v>97062</v>
+        <v>57509</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,25 +910,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517750</v>
+        <v>517751</v>
       </c>
       <c r="R4" t="n">
-        <v>6710311</v>
+        <v>6710312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 6972-2022 artfynd.xlsx
+++ b/artfynd/A 6972-2022 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285680</v>
+        <v>121285681</v>
       </c>
       <c r="B3" t="n">
-        <v>97062</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517750</v>
+        <v>517751</v>
       </c>
       <c r="R3" t="n">
-        <v>6710311</v>
+        <v>6710312</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285681</v>
+        <v>121285680</v>
       </c>
       <c r="B4" t="n">
-        <v>57509</v>
+        <v>97062</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,25 +910,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517751</v>
+        <v>517750</v>
       </c>
       <c r="R4" t="n">
-        <v>6710312</v>
+        <v>6710311</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 6972-2022 artfynd.xlsx
+++ b/artfynd/A 6972-2022 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285681</v>
+        <v>121285680</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>97067</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517751</v>
+        <v>517750</v>
       </c>
       <c r="R3" t="n">
-        <v>6710312</v>
+        <v>6710311</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121285680</v>
+        <v>121285681</v>
       </c>
       <c r="B4" t="n">
-        <v>97062</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,25 +910,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517750</v>
+        <v>517751</v>
       </c>
       <c r="R4" t="n">
-        <v>6710311</v>
+        <v>6710312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
